--- a/docs/gantt(2).xlsx
+++ b/docs/gantt(2).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\aboba\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF14BA0-342A-447D-8657-97292342DB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9C6BE9-175E-4DBE-99B8-3B2E3F8E9310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Гантт" sheetId="1" r:id="rId1"/>
@@ -568,7 +568,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
@@ -576,7 +576,7 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -594,7 +594,7 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -611,7 +611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -628,7 +628,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -642,10 +642,10 @@
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -659,10 +659,10 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -676,10 +676,10 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -696,7 +696,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -713,7 +713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -730,7 +730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -747,7 +747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -781,7 +781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -798,7 +798,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -815,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -832,12 +832,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>50</v>
       </c>
